--- a/Evaluasi_Skenario_Trade.xlsx
+++ b/Evaluasi_Skenario_Trade.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="7">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -51,6 +51,12 @@
     <font>
       <name val="Calibri"/>
       <b val="1"/>
+      <color rgb="001D4ED8"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="0015803D"/>
       <sz val="10"/>
     </font>
@@ -60,8 +66,14 @@
       <color rgb="00B91C1C"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="006B7280"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -76,8 +88,20 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
+        <bgColor rgb="00DBEAFE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
         <bgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D97706"/>
+        <bgColor rgb="00D97706"/>
       </patternFill>
     </fill>
     <fill>
@@ -90,12 +114,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F3F4F6"/>
         <bgColor rgb="00F3F4F6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00D97706"/>
-        <bgColor rgb="00D97706"/>
       </patternFill>
     </fill>
   </fills>
@@ -125,7 +143,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -138,17 +156,20 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -515,37 +536,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="117" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="28" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📊 MATRIKS EVALUASI PERFORMA SKENARIO TRADING (PENGUJIAN 5 - 10X)</t>
+          <t>📊 MATRIKS EVALUASI PERFORMA SKENARIO (BEP 75m + Tracker WIN/LOSS 10x)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Sistem cerdas menapis skenario: Pola unggulan dipertahankan, pola yang sering loss otomatis dihindari/diblacklist.</t>
+          <t>WIN Efektif = WIN Murni + BEP Rebound (arah prediksi terbukti). Milestone 10x: 🌟 ANDAL atau ⚠️ RETRAIN DIPERLUKAN.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="28" customHeight="1">
+    <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
           <t>Skenario Entry</t>
@@ -558,40 +583,60 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Menang (WIN)</t>
+          <t>Menang Murni (WIN)</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>BEP Rebound (Arah Valid)</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>BEP Netral (Shield)</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
           <t>Kalah (LOSS)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>Impas (BEP)</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>Win Rate (%)</t>
-        </is>
-      </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
+          <t>Win Rate Efektif (%)</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
           <t>Total PnL ($ USD)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Rata-rata PnL ($)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Tracker Win 10x</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>Tracker Loss 10x</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>Milestone</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>Status Evaluasi Skenario</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>Tindakan Bot</t>
         </is>
@@ -600,266 +645,56 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Diag_BUY</t>
+          <t>GENERAL_ENTRY</t>
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="D5" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="E5" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="5" t="n">
-        <v>0</v>
-      </c>
       <c r="F5" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>-8.029999999999999</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>-2.68</v>
-      </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>⏳ DALAM PENGUJIAN (3/5 Trade)</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>73.7</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>34.99</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.92</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>ALLOW_TESTING</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_A-Diag_SELL</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>⏳ DALAM PENGUJIAN (1/5 Trade)</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>ALLOW_TESTING</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="C7" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="D7" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>60</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>-13.45</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>-2.69</v>
-      </c>
-      <c r="I7" s="7" t="inlineStr">
-        <is>
-          <t>⛔ SKENARIO DIHINDARI (Banyak Loss / Dilarang)</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>BLACKLIST_AVOID</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="5" t="n">
-        <v>5</v>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>83.3</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>17.2</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="I8" s="8" t="inlineStr">
+          <t>[28/10 Win]</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
+          <t>[9/10 Loss]</t>
+        </is>
+      </c>
+      <c r="L5" s="6" t="inlineStr">
+        <is>
+          <t>🌟 ANDAL (&gt;=10x Win Valid)</t>
+        </is>
+      </c>
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>🌟 SKENARIO UNGGULAN (Rekomendasi Entry)</t>
         </is>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="N5" s="4" t="inlineStr">
         <is>
           <t>ALLOW_AND_BOOST</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_C_SELL</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C9" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="D9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="5" t="n">
-        <v>100</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>⏳ DALAM PENGUJIAN (1/5 Trade)</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>ALLOW_TESTING</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="5" t="n">
-        <v>66.7</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>5.86</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="I10" s="8" t="inlineStr">
-        <is>
-          <t>🌟 SKENARIO UNGGULAN (Rekomendasi Entry)</t>
-        </is>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>ALLOW_AND_BOOST</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>M5_ZONA_A-Diag_SELL</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D11" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>⏳ DALAM PENGUJIAN (1/5 Trade)</t>
-        </is>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>ALLOW_TESTING</t>
         </is>
       </c>
     </row>
@@ -874,2682 +709,4753 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y27"/>
+  <dimension ref="A1:AB42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
+    <col width="55" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="17" customWidth="1" min="9" max="9"/>
-    <col width="19" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="17" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
-    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="49" customWidth="1" min="12" max="12"/>
     <col width="17" customWidth="1" min="13" max="13"/>
-    <col width="14" customWidth="1" min="14" max="14"/>
-    <col width="27" customWidth="1" min="15" max="15"/>
-    <col width="45" customWidth="1" min="16" max="16"/>
-    <col width="24" customWidth="1" min="17" max="17"/>
-    <col width="16" customWidth="1" min="18" max="18"/>
-    <col width="16" customWidth="1" min="19" max="19"/>
-    <col width="17" customWidth="1" min="20" max="20"/>
-    <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="25" customWidth="1" min="22" max="22"/>
-    <col width="45" customWidth="1" min="23" max="23"/>
-    <col width="45" customWidth="1" min="24" max="24"/>
-    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="15" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="17" customWidth="1" min="16" max="16"/>
+    <col width="21" customWidth="1" min="17" max="17"/>
+    <col width="25" customWidth="1" min="18" max="18"/>
+    <col width="55" customWidth="1" min="19" max="19"/>
+    <col width="55" customWidth="1" min="20" max="20"/>
+    <col width="22" customWidth="1" min="21" max="21"/>
+    <col width="23" customWidth="1" min="22" max="22"/>
+    <col width="24" customWidth="1" min="23" max="23"/>
+    <col width="17" customWidth="1" min="24" max="24"/>
+    <col width="14" customWidth="1" min="25" max="25"/>
+    <col width="17" customWidth="1" min="26" max="26"/>
+    <col width="19" customWidth="1" min="27" max="27"/>
+    <col width="31" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>📝 LOG ANALISIS MENDALAM KEMENANGAN &amp; KESALAHAN PER TRADE</t>
+          <t>📝 LOG ANALISIS MENDALAM PER TRADE (WIN / LOSS / BEP REBOUND / BEP NETRAL)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Mencatat diagnosa teknikal SMC, tren H4, DXY, dan kondisi makroekonomi untuk setiap posisi.</t>
+          <t>Diagnosa dinamis kontekstual: evaluasi candle ke-5 (75m), tren H4/DXY, makroekonomi, milestone tracker 10x.</t>
         </is>
       </c>
     </row>
     <row r="3"/>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="9" t="inlineStr">
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
         <is>
           <t>Ticket Posisi</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>Waktu Open</t>
         </is>
       </c>
-      <c r="C4" s="9" t="inlineStr">
+      <c r="C4" s="8" t="inlineStr">
         <is>
           <t>Waktu Close</t>
         </is>
       </c>
-      <c r="D4" s="9" t="inlineStr">
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>Simbol</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>Tipe</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>Lot</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>Harga Entry</t>
+        </is>
+      </c>
+      <c r="H4" s="8" t="inlineStr">
+        <is>
+          <t>Harga Exit</t>
+        </is>
+      </c>
+      <c r="I4" s="8" t="inlineStr">
+        <is>
+          <t>Pips (P/L)</t>
+        </is>
+      </c>
+      <c r="J4" s="8" t="inlineStr">
+        <is>
+          <t>Profit ($ USD)</t>
+        </is>
+      </c>
+      <c r="K4" s="8" t="inlineStr">
+        <is>
+          <t>Hasil</t>
+        </is>
+      </c>
+      <c r="L4" s="8" t="inlineStr">
+        <is>
+          <t>Model AI</t>
+        </is>
+      </c>
+      <c r="M4" s="8" t="inlineStr">
+        <is>
+          <t>Skenario Entry</t>
+        </is>
+      </c>
+      <c r="N4" s="8" t="inlineStr">
+        <is>
+          <t>Zona Entry</t>
+        </is>
+      </c>
+      <c r="O4" s="8" t="inlineStr">
+        <is>
+          <t>Tren H4 Entry</t>
+        </is>
+      </c>
+      <c r="P4" s="8" t="inlineStr">
+        <is>
+          <t>Tren DXY Entry</t>
+        </is>
+      </c>
+      <c r="Q4" s="8" t="inlineStr">
+        <is>
+          <t>Kondisi Makro News</t>
+        </is>
+      </c>
+      <c r="R4" s="8" t="inlineStr">
+        <is>
+          <t>Probabilitas Model (%)</t>
+        </is>
+      </c>
+      <c r="S4" s="8" t="inlineStr">
+        <is>
+          <t>Analisis Diagnostik (Menang/Kalah)</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>Evaluasi &amp; Pembelajaran</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>Tanggal Evaluasi</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>Close Candle 75m ($)</t>
+        </is>
+      </c>
+      <c r="W4" s="8" t="inlineStr">
+        <is>
+          <t>Validasi Model 75M</t>
+        </is>
+      </c>
+      <c r="X4" s="8" t="inlineStr">
+        <is>
+          <t>Pips Model 75M</t>
+        </is>
+      </c>
+      <c r="Y4" s="8" t="inlineStr">
         <is>
           <t>Durasi</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
-        <is>
-          <t>Simbol</t>
-        </is>
-      </c>
-      <c r="F4" s="9" t="inlineStr">
-        <is>
-          <t>Tipe</t>
-        </is>
-      </c>
-      <c r="G4" s="9" t="inlineStr">
-        <is>
-          <t>Lot</t>
-        </is>
-      </c>
-      <c r="H4" s="9" t="inlineStr">
-        <is>
-          <t>Harga Entry</t>
-        </is>
-      </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="Z4" s="8" t="inlineStr">
         <is>
           <t>Stop Loss (SL)</t>
         </is>
       </c>
-      <c r="J4" s="9" t="inlineStr">
+      <c r="AA4" s="8" t="inlineStr">
         <is>
           <t>Take Profit (TP)</t>
         </is>
       </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>Harga Exit</t>
-        </is>
-      </c>
-      <c r="L4" s="9" t="inlineStr">
-        <is>
-          <t>Pips (P/L)</t>
-        </is>
-      </c>
-      <c r="M4" s="9" t="inlineStr">
-        <is>
-          <t>Profit ($ USD)</t>
-        </is>
-      </c>
-      <c r="N4" s="9" t="inlineStr">
-        <is>
-          <t>Hasil</t>
-        </is>
-      </c>
-      <c r="O4" s="9" t="inlineStr">
+      <c r="AB4" s="8" t="inlineStr">
         <is>
           <t>Keterangan / Alasan Exit</t>
-        </is>
-      </c>
-      <c r="P4" s="9" t="inlineStr">
-        <is>
-          <t>Model AI</t>
-        </is>
-      </c>
-      <c r="Q4" s="9" t="inlineStr">
-        <is>
-          <t>Skenario Entry</t>
-        </is>
-      </c>
-      <c r="R4" s="9" t="inlineStr">
-        <is>
-          <t>Zona Entry</t>
-        </is>
-      </c>
-      <c r="S4" s="9" t="inlineStr">
-        <is>
-          <t>Tren H4 Entry</t>
-        </is>
-      </c>
-      <c r="T4" s="9" t="inlineStr">
-        <is>
-          <t>Tren DXY Entry</t>
-        </is>
-      </c>
-      <c r="U4" s="9" t="inlineStr">
-        <is>
-          <t>Kondisi Makro News</t>
-        </is>
-      </c>
-      <c r="V4" s="9" t="inlineStr">
-        <is>
-          <t>Probabilitas Model (%)</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>Analisis Diagnostik (Menang/Kalah)</t>
-        </is>
-      </c>
-      <c r="X4" s="9" t="inlineStr">
-        <is>
-          <t>Evaluasi &amp; Pembelajaran</t>
-        </is>
-      </c>
-      <c r="Y4" s="9" t="inlineStr">
-        <is>
-          <t>Tanggal Evaluasi</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>2573313197</v>
+        <v>2660594060</v>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 22:14:55</t>
+          <t>2026-10-08 02:00:00</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 22:38:46</t>
+          <t>2026-10-08 02:08:19</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>23m 51d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F5" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F5" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G5" s="4" t="n">
-        <v>0.01</v>
+        <v>4109.353999999999</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>4352.281</v>
+        <v>4102.85</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>4345.281</v>
+        <v>-65</v>
       </c>
       <c r="J5" s="4" t="n">
-        <v>4369.781</v>
-      </c>
-      <c r="K5" s="4" t="n">
-        <v>4352.481</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N5" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-6.5</v>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L5" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M5" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N5" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q5" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S5" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4102.85 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 8m 19d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U5" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 02:15:03</t>
+        </is>
+      </c>
+      <c r="V5" s="4" t="n">
+        <v>4107.02</v>
+      </c>
+      <c r="W5" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X5" s="4" t="n">
+        <v>-23.3</v>
+      </c>
+      <c r="Y5" s="4" t="inlineStr">
+        <is>
+          <t>8m 19d</t>
+        </is>
+      </c>
+      <c r="Z5" s="4" t="n">
+        <v>4102.85</v>
+      </c>
+      <c r="AA5" s="4" t="n">
+        <v>4117.85</v>
+      </c>
+      <c r="AB5" s="4" t="inlineStr">
+        <is>
           <t>Hit Stop Loss (SL)</t>
-        </is>
-      </c>
-      <c r="P5" s="4" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
-        </is>
-      </c>
-      <c r="Q5" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R5" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
-      </c>
-      <c r="S5" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U5" s="4" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="V5" s="4" t="n">
-        <v>50</v>
-      </c>
-      <c r="W5" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X5" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-22 21:31:03</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="n">
-        <v>2573549087</v>
+        <v>2660642498</v>
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 22:59:55</t>
+          <t>2026-10-08 02:15:01</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-18 23:29:18</t>
+          <t>2026-10-08 02:25:52</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>29m 23d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F6" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F6" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G6" s="4" t="n">
-        <v>0.01</v>
+        <v>4107.19</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>4356.893</v>
+        <v>4107.39</v>
       </c>
       <c r="I6" s="4" t="n">
-        <v>4349.893</v>
+        <v>2</v>
       </c>
       <c r="J6" s="4" t="n">
-        <v>4374.393</v>
-      </c>
-      <c r="K6" s="4" t="n">
-        <v>4374.393</v>
-      </c>
-      <c r="L6" s="4" t="n">
-        <v>175</v>
-      </c>
-      <c r="M6" s="4" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>0.2</v>
+      </c>
+      <c r="K6" s="10" t="inlineStr">
+        <is>
+          <t>BEP_NETRAL</t>
+        </is>
+      </c>
+      <c r="L6" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+      <c r="M6" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N6" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Hit Take Profit (TP)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q6" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R6" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S6" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>🛡️ [BEP NETRAL — Penyelamat Modal, Arah Gagal]: Auto Break-Even (+0.20) MENYELAMATKAN dari potensi kerugian: pada candle ke-5 (2026-10-08 02:30), harga close $4105.06 (di BAWAH entry $4107.19, -21.3 pip) — berlawanan dengan prediksi model | Fitur Auto-BEP berfungsi optimal sebagai shield pelindung modal — skenario GENERAL_ENTRY.</t>
         </is>
       </c>
       <c r="T6" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Pada skenario GENERAL_ENTRY, prediksi model tidak terkonfirmasi dalam 75 menit. Evaluasi kondisi masuk: pastikan momentum H4 lebih kuat. Auto-BEP berhasil melindungi modal dari kerugian yang lebih besar.</t>
         </is>
       </c>
       <c r="U6" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 02:41:36</t>
         </is>
       </c>
       <c r="V6" s="4" t="n">
-        <v>50</v>
+        <v>4105.06</v>
       </c>
       <c r="W6" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Target Take Profit (TP) tercapai penuh secara sniper</t>
-        </is>
-      </c>
-      <c r="X6" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X6" s="4" t="n">
+        <v>-21.3</v>
       </c>
       <c r="Y6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:31:12</t>
+          <t>10m 51d</t>
+        </is>
+      </c>
+      <c r="Z6" s="4" t="n">
+        <v>4100.69</v>
+      </c>
+      <c r="AA6" s="4" t="n">
+        <v>4115.69</v>
+      </c>
+      <c r="AB6" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="n">
-        <v>2573977759</v>
+        <v>2660695397</v>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 00:14:54</t>
+          <t>2026-10-08 02:45:01</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-19 00:34:25</t>
+          <t>2026-10-08 03:31:00</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>19m 31d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F7" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>0.01</v>
+        <v>4104.599999999999</v>
       </c>
       <c r="H7" s="4" t="n">
-        <v>4385.443</v>
+        <v>4113.1</v>
       </c>
       <c r="I7" s="4" t="n">
-        <v>4392.443</v>
+        <v>85</v>
       </c>
       <c r="J7" s="4" t="n">
-        <v>4374.283</v>
-      </c>
-      <c r="K7" s="4" t="n">
-        <v>4392.443</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>-70</v>
-      </c>
-      <c r="M7" s="4" t="n">
-        <v>-7</v>
-      </c>
-      <c r="N7" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>8.5</v>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L7" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+      <c r="M7" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N7" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M5 v4.1 (Wide SL + Sniper + Anti-Repeat)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q7" s="4" t="inlineStr">
         <is>
-          <t>M5_ZONA_A-Diag_SELL</t>
-        </is>
-      </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R7" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S7" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>✅ [WIN — Kemenangan Target]: Target Take Profit (TP) $4113.10 tercapai penuh dalam 45m 59d | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4109.54, deviasi +49.4 pip searah BUY).</t>
         </is>
       </c>
       <c r="T7" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U7" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 03:48:38</t>
         </is>
       </c>
       <c r="V7" s="4" t="n">
-        <v>50</v>
+        <v>4109.54</v>
       </c>
       <c r="W7" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh</t>
-        </is>
-      </c>
-      <c r="X7" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X7" s="4" t="n">
+        <v>49.4</v>
       </c>
       <c r="Y7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 23:23:10</t>
+          <t>45m 59d</t>
+        </is>
+      </c>
+      <c r="Z7" s="4" t="n">
+        <v>4098.1</v>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>4113.1</v>
+      </c>
+      <c r="AB7" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="n">
-        <v>2577450981</v>
+        <v>2660925999</v>
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 07:44:54</t>
+          <t>2026-10-08 05:15:02</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 07:51:02</t>
+          <t>2026-10-08 06:29:02</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>6m 8d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F8" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F8" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G8" s="4" t="n">
-        <v>0.01</v>
+        <v>4108.353</v>
       </c>
       <c r="H8" s="4" t="n">
-        <v>4368.619</v>
+        <v>4109.202</v>
       </c>
       <c r="I8" s="4" t="n">
-        <v>4363.431</v>
+        <v>8.5</v>
       </c>
       <c r="J8" s="4" t="n">
-        <v>4380.931</v>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>4362.783</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>-58.4</v>
-      </c>
-      <c r="M8" s="4" t="n">
-        <v>-5.84</v>
-      </c>
-      <c r="N8" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>0.85</v>
+      </c>
+      <c r="K8" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM M15 v3.7 (Wide SL + RRR 2.5 + Sniper)</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R8" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R8" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S8" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Posisi ditutup profit $0.85 di $4109.20 (+8.5 pip dari entry $4108.35) | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4111.89, deviasi +35.4 pip searah BUY).</t>
         </is>
       </c>
       <c r="T8" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U8" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 11:24:54</t>
         </is>
       </c>
       <c r="V8" s="4" t="n">
-        <v>71.9291557458769</v>
+        <v>4111.89</v>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X8" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X8" s="4" t="n">
+        <v>35.4</v>
       </c>
       <c r="Y8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:31:22</t>
+          <t>1j 14m</t>
+        </is>
+      </c>
+      <c r="Z8" s="4" t="n">
+        <v>4101.85</v>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>4116.85</v>
+      </c>
+      <c r="AB8" s="4" t="inlineStr">
+        <is>
+          <t>Close_Thesis 75M Horizon E</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="n">
-        <v>2579837091</v>
+        <v>2662267752</v>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 15:44:54</t>
+          <t>2026-10-08 11:45:00</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21 15:54:56</t>
+          <t>2026-10-08 12:00:00</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>10m 2d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F9" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F9" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G9" s="4" t="n">
-        <v>0.01</v>
+        <v>4132.79</v>
       </c>
       <c r="H9" s="4" t="n">
-        <v>4357.664</v>
+        <v>4132.99</v>
       </c>
       <c r="I9" s="4" t="n">
-        <v>4351.264</v>
+        <v>2</v>
       </c>
       <c r="J9" s="4" t="n">
-        <v>4373.664</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>4351.264</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>-64</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="N9" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>0.2</v>
+      </c>
+      <c r="K9" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R9" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R9" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S9" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-08 12:15), harga close $4132.70 (di ATAS entry $4132.79, +0.9 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T9" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U9" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 12:16:47</t>
         </is>
       </c>
       <c r="V9" s="4" t="n">
-        <v>81.24885709548593</v>
+        <v>4132.7</v>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X9" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X9" s="4" t="n">
+        <v>-0.9</v>
       </c>
       <c r="Y9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:31:33</t>
+          <t>15m 0d</t>
+        </is>
+      </c>
+      <c r="Z9" s="4" t="n">
+        <v>4126.29</v>
+      </c>
+      <c r="AA9" s="4" t="n">
+        <v>4141.29</v>
+      </c>
+      <c r="AB9" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="n">
-        <v>2583401048</v>
+        <v>2663920669</v>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 03:29:55</t>
+          <t>2026-10-08 18:00:00</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 05:08:10</t>
+          <t>2026-10-08 18:12:47</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>1j 38m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F10" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>0.01</v>
+        <v>4121.999</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>4340.675</v>
+        <v>4117.5</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>4336.175</v>
+        <v>45</v>
       </c>
       <c r="J10" s="4" t="n">
-        <v>4349.675</v>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>4349.675</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>90</v>
-      </c>
-      <c r="M10" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
+        <v>4.5</v>
+      </c>
+      <c r="K10" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>Hit Take Profit (TP)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q10" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R10" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R10" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S10" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +45.0 pip (exit di $4117.50) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4116.83, deviasi +51.7 pip searah SELL).</t>
         </is>
       </c>
       <c r="T10" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U10" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 18:12:49</t>
         </is>
       </c>
       <c r="V10" s="4" t="n">
-        <v>57.21569387806662</v>
+        <v>4116.83</v>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Target Take Profit (TP) tercapai penuh secara sniper</t>
-        </is>
-      </c>
-      <c r="X10" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X10" s="4" t="n">
+        <v>51.7</v>
       </c>
       <c r="Y10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:31:44</t>
+          <t>12m 47d</t>
+        </is>
+      </c>
+      <c r="Z10" s="4" t="n">
+        <v>4128.5</v>
+      </c>
+      <c r="AA10" s="4" t="n">
+        <v>4113.5</v>
+      </c>
+      <c r="AB10" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="n">
-        <v>2584927512</v>
+        <v>2664053568</v>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 11:14:55</t>
+          <t>2026-10-08 18:30:01</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 12:19:50</t>
+          <t>2026-10-08 18:37:10</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>1j 4m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F11" s="4" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>0.01</v>
+        <v>4123.873000000001</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>4339.094</v>
+        <v>4121.87</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>4332.394</v>
+        <v>20</v>
       </c>
       <c r="J11" s="4" t="n">
-        <v>4355.894</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>4339.294</v>
-      </c>
-      <c r="L11" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M11" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
+      <c r="K11" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q11" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="R11" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Horiz</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R11" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S11" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4121.87) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4123.10, deviasi +7.7 pip searah SELL).</t>
         </is>
       </c>
       <c r="T11" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U11" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 18:45:15</t>
         </is>
       </c>
       <c r="V11" s="4" t="n">
-        <v>52.2535354662066</v>
+        <v>4123.1</v>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X11" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X11" s="4" t="n">
+        <v>7.7</v>
       </c>
       <c r="Y11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:31:53</t>
+          <t>7m 9d</t>
+        </is>
+      </c>
+      <c r="Z11" s="4" t="n">
+        <v>4130.37</v>
+      </c>
+      <c r="AA11" s="4" t="n">
+        <v>4115.37</v>
+      </c>
+      <c r="AB11" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="n">
-        <v>2585747588</v>
+        <v>2664449281</v>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 13:59:55</t>
+          <t>2026-10-08 19:45:00</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 14:28:34</t>
+          <t>2026-10-08 20:02:49</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>28m 39d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F12" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G12" s="4" t="n">
-        <v>0.01</v>
+        <v>4119.594</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>4318.927</v>
+        <v>4117.075</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>4311.927</v>
+        <v>-25.2</v>
       </c>
       <c r="J12" s="4" t="n">
-        <v>4336.427</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>4319.127</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M12" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N12" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-2.51</v>
+      </c>
+      <c r="K12" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q12" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Horiz</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R12" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S12" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>❌ [LOSS — Analisis Kesalahan]: AI Early Cut-Loss diaktifkan di $4117.07 — sinyal pembalikan arah terdeteksi sebelum SL penuh tersentuh | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
         </is>
       </c>
       <c r="T12" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
         </is>
       </c>
       <c r="U12" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 20:02:51</t>
         </is>
       </c>
       <c r="V12" s="4" t="n">
-        <v>52.68443260043703</v>
+        <v>4117.38</v>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X12" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X12" s="4" t="n">
+        <v>-22.1</v>
       </c>
       <c r="Y12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 21:32:02</t>
+          <t>17m 49d</t>
+        </is>
+      </c>
+      <c r="Z12" s="4" t="n">
+        <v>4113.09</v>
+      </c>
+      <c r="AA12" s="4" t="n">
+        <v>4128.09</v>
+      </c>
+      <c r="AB12" s="4" t="inlineStr">
+        <is>
+          <t>AI Early Cut-Loss (Reversal)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="n">
-        <v>2587188646</v>
+        <v>2664981406</v>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 17:59:55</t>
+          <t>2026-10-08 21:00:00</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22 18:55:35</t>
+          <t>2026-10-08 21:04:02</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>55m 40d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>0.01</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>0.01</v>
+        <v>4130.319</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>4322.68</v>
+        <v>4123.82</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>4329.969</v>
+        <v>-65</v>
       </c>
       <c r="J13" s="4" t="n">
-        <v>4305.469</v>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>4322.48</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M13" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-6.5</v>
+      </c>
+      <c r="K13" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R13" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4123.82 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 4m 2d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 21:04:03</t>
+        </is>
+      </c>
+      <c r="V13" s="4" t="n">
+        <v>4123.7</v>
+      </c>
+      <c r="W13" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X13" s="4" t="n">
+        <v>-66.2</v>
+      </c>
+      <c r="Y13" s="4" t="inlineStr">
+        <is>
+          <t>4m 2d</t>
+        </is>
+      </c>
+      <c r="Z13" s="4" t="n">
+        <v>4123.82</v>
+      </c>
+      <c r="AA13" s="4" t="n">
+        <v>4138.82</v>
+      </c>
+      <c r="AB13" s="4" t="inlineStr">
+        <is>
           <t>Hit Stop Loss (SL)</t>
-        </is>
-      </c>
-      <c r="P13" s="4" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_A-Diag_SELL</t>
-        </is>
-      </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Diag</t>
-        </is>
-      </c>
-      <c r="S13" s="4" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="T13" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U13" s="4" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="V13" s="4" t="n">
-        <v>52.38734967430565</v>
-      </c>
-      <c r="W13" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif | Didukung penuh tren besar H4 (Searah Trend Institusional)</t>
-        </is>
-      </c>
-      <c r="X13" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
-      </c>
-      <c r="Y13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-22 21:32:12</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="n">
-        <v>2591745453</v>
+        <v>2665072695</v>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 14:29:55</t>
+          <t>2026-10-08 21:15:00</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:10:44</t>
+          <t>2026-10-08 21:20:47</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>40m 49d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F14" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G14" s="4" t="n">
-        <v>0.01</v>
+        <v>4123.753</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>4324.741</v>
+        <v>4132.25</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>4317.487</v>
+        <v>85</v>
       </c>
       <c r="J14" s="4" t="n">
-        <v>4342.687</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>4317.487</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>-72.5</v>
-      </c>
-      <c r="M14" s="4" t="n">
-        <v>-7.25</v>
-      </c>
-      <c r="N14" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>8.5</v>
+      </c>
+      <c r="K14" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="R14" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Horiz</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R14" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S14" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Target Take Profit (TP) $4132.25 tercapai penuh dalam 5m 47d | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4132.35, deviasi +86.0 pip searah BUY).</t>
         </is>
       </c>
       <c r="T14" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U14" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 21:20:49</t>
         </is>
       </c>
       <c r="V14" s="4" t="n">
-        <v>57.21425923786786</v>
+        <v>4132.35</v>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X14" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X14" s="4" t="n">
+        <v>86</v>
       </c>
       <c r="Y14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 15:10:45</t>
+          <t>5m 47d</t>
+        </is>
+      </c>
+      <c r="Z14" s="4" t="n">
+        <v>4117.25</v>
+      </c>
+      <c r="AA14" s="4" t="n">
+        <v>4132.25</v>
+      </c>
+      <c r="AB14" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="n">
-        <v>2592236187</v>
+        <v>2665174675</v>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44:54</t>
+          <t>2026-10-08 21:30:00</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:48:34</t>
+          <t>2026-10-08 21:35:11</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>3m 40d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F15" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F15" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G15" s="4" t="n">
-        <v>0.01</v>
+        <v>4137.061</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>4316.467</v>
+        <v>4137.26</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>4309.667</v>
+        <v>2</v>
       </c>
       <c r="J15" s="4" t="n">
-        <v>4333.467</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>4309.667</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>-68</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>-6.8</v>
-      </c>
-      <c r="N15" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>0.2</v>
+      </c>
+      <c r="K15" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="R15" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Horiz</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R15" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S15" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-08 21:30), harga close $4137.24 (di ATAS entry $4137.06, +1.8 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T15" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U15" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 21:35:14</t>
         </is>
       </c>
       <c r="V15" s="4" t="n">
-        <v>51.10519658893553</v>
+        <v>4137.24</v>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X15" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X15" s="4" t="n">
+        <v>1.8</v>
       </c>
       <c r="Y15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:48:35</t>
+          <t>5m 11d</t>
+        </is>
+      </c>
+      <c r="Z15" s="4" t="n">
+        <v>4130.56</v>
+      </c>
+      <c r="AA15" s="4" t="n">
+        <v>4145.56</v>
+      </c>
+      <c r="AB15" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="n">
-        <v>2592746187</v>
+        <v>2665291192</v>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 18:44:54</t>
+          <t>2026-10-08 21:45:00</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 18:48:07</t>
+          <t>2026-10-08 22:01:32</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>3m 13d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F16" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G16" s="4" t="n">
-        <v>0.01</v>
+        <v>4126.428</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>4304.452</v>
+        <v>4119.93</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>4297.352</v>
+        <v>-65</v>
       </c>
       <c r="J16" s="4" t="n">
-        <v>4322.252</v>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>4304.652</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M16" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-6.5</v>
+      </c>
+      <c r="K16" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R16" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4119.93 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 16m 32d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-08 22:01:33</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="n">
+        <v>4120.13</v>
+      </c>
+      <c r="W16" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X16" s="4" t="n">
+        <v>-63</v>
+      </c>
+      <c r="Y16" s="4" t="inlineStr">
+        <is>
+          <t>16m 32d</t>
+        </is>
+      </c>
+      <c r="Z16" s="4" t="n">
+        <v>4119.93</v>
+      </c>
+      <c r="AA16" s="4" t="n">
+        <v>4134.93</v>
+      </c>
+      <c r="AB16" s="4" t="inlineStr">
+        <is>
           <t>Hit Stop Loss (SL)</t>
-        </is>
-      </c>
-      <c r="P16" s="4" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_A-Horiz_BUY</t>
-        </is>
-      </c>
-      <c r="R16" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Horiz</t>
-        </is>
-      </c>
-      <c r="S16" s="4" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="T16" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U16" s="4" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="V16" s="4" t="n">
-        <v>55.92949657222967</v>
-      </c>
-      <c r="W16" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X16" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
-      </c>
-      <c r="Y16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-23 18:48:08</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="n">
-        <v>2592820420</v>
+        <v>2665474009</v>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 18:59:55</t>
+          <t>2026-10-08 22:15:00</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:30:14</t>
+          <t>2026-10-08 22:45:33</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>30m 19d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F17" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G17" s="4" t="n">
-        <v>0.01</v>
+        <v>4115.503</v>
       </c>
       <c r="H17" s="4" t="n">
-        <v>4309.479</v>
+        <v>4115.7</v>
       </c>
       <c r="I17" s="4" t="n">
-        <v>4303.079</v>
+        <v>2</v>
       </c>
       <c r="J17" s="4" t="n">
-        <v>4322.279</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>4309.679</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M17" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N17" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R17" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R17" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S17" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-08 22:45), harga close $4115.52 (di ATAS entry $4115.50, +0.2 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T17" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U17" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 22:45:34</t>
         </is>
       </c>
       <c r="V17" s="4" t="n">
-        <v>58.14266687195159</v>
+        <v>4115.52</v>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X17" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X17" s="4" t="n">
+        <v>0.2</v>
       </c>
       <c r="Y17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:33:03</t>
+          <t>30m 33d</t>
+        </is>
+      </c>
+      <c r="Z17" s="4" t="n">
+        <v>4109</v>
+      </c>
+      <c r="AA17" s="4" t="n">
+        <v>4126.5</v>
+      </c>
+      <c r="AB17" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
-        <v>2593179348</v>
+        <v>2665706182</v>
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 19:59:54</t>
+          <t>2026-10-08 23:00:01</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 20:08:03</t>
+          <t>2026-10-08 23:17:17</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>8m 9d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F18" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F18" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G18" s="4" t="n">
-        <v>0.01</v>
+        <v>4111.735</v>
       </c>
       <c r="H18" s="4" t="n">
-        <v>4310.338</v>
+        <v>4122.68</v>
       </c>
       <c r="I18" s="4" t="n">
-        <v>4302.738</v>
+        <v>109.5</v>
       </c>
       <c r="J18" s="4" t="n">
-        <v>4325.538</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>4302.738</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>-76</v>
-      </c>
-      <c r="M18" s="4" t="n">
-        <v>-7.6</v>
-      </c>
-      <c r="N18" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>10.94</v>
+      </c>
+      <c r="K18" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Wide SL + RRR 2.5 + Sniper)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R18" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R18" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S18" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Target Take Profit (TP) $4122.68 tercapai penuh dalam 17m 16d | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4123.53, deviasi +118.0 pip searah BUY).</t>
         </is>
       </c>
       <c r="T18" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U18" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 23:17:20</t>
         </is>
       </c>
       <c r="V18" s="4" t="n">
-        <v>60.33016693799478</v>
+        <v>4123.53</v>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X18" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X18" s="4" t="n">
+        <v>118</v>
       </c>
       <c r="Y18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-23 20:08:05</t>
+          <t>17m 16d</t>
+        </is>
+      </c>
+      <c r="Z18" s="4" t="n">
+        <v>4105.18</v>
+      </c>
+      <c r="AA18" s="4" t="n">
+        <v>4122.68</v>
+      </c>
+      <c r="AB18" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="n">
-        <v>2595301847</v>
+        <v>2665949951</v>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 02:59:55</t>
+          <t>2026-10-08 23:30:00</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 06:43:32</t>
+          <t>2026-10-08 23:33:53</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>3j 43m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F19" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F19" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G19" s="4" t="n">
-        <v>0.01</v>
+        <v>4117.652</v>
       </c>
       <c r="H19" s="4" t="n">
-        <v>4284.755</v>
+        <v>4117.85</v>
       </c>
       <c r="I19" s="4" t="n">
-        <v>4276.255</v>
+        <v>2</v>
       </c>
       <c r="J19" s="4" t="n">
-        <v>4305.955</v>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>4284.955</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M19" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N19" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K19" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q19" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R19" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S19" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-08 23:30), harga close $4119.31 (di ATAS entry $4117.65, +16.6 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T19" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U19" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-08 23:33:55</t>
         </is>
       </c>
       <c r="V19" s="4" t="n">
-        <v>71.67923417777037</v>
+        <v>4119.31</v>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X19" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X19" s="4" t="n">
+        <v>16.6</v>
       </c>
       <c r="Y19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 06:43:33</t>
+          <t>3m 53d</t>
+        </is>
+      </c>
+      <c r="Z19" s="4" t="n">
+        <v>4111.09</v>
+      </c>
+      <c r="AA19" s="4" t="n">
+        <v>4126.09</v>
+      </c>
+      <c r="AB19" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="n">
-        <v>2596572850</v>
+        <v>2666333428</v>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 11:14:55</t>
+          <t>2026-10-09 00:30:00</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 12:31:55</t>
+          <t>2026-10-09 01:03:49</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>1j 17m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F20" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F20" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G20" s="4" t="n">
-        <v>0.01</v>
+        <v>4131.308</v>
       </c>
       <c r="H20" s="4" t="n">
-        <v>4285.272</v>
+        <v>4131.51</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>4276.772</v>
+        <v>2</v>
       </c>
       <c r="J20" s="4" t="n">
-        <v>4306.472</v>
-      </c>
-      <c r="K20" s="4" t="n">
-        <v>4285.472</v>
-      </c>
-      <c r="L20" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M20" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N20" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q20" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_C_SNIPER_BUY</t>
-        </is>
-      </c>
-      <c r="R20" s="4" t="inlineStr">
-        <is>
-          <t>Zona C_SNIPER</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R20" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S20" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-09 01:00), harga close $4131.28 (di ATAS entry $4131.31, +0.3 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T20" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U20" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 01:03:50</t>
         </is>
       </c>
       <c r="V20" s="4" t="n">
-        <v>71.49298235225024</v>
+        <v>4131.28</v>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X20" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X20" s="4" t="n">
+        <v>-0.3</v>
       </c>
       <c r="Y20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 12:31:58</t>
+          <t>33m 49d</t>
+        </is>
+      </c>
+      <c r="Z20" s="4" t="n">
+        <v>4124.7</v>
+      </c>
+      <c r="AA20" s="4" t="n">
+        <v>4139.7</v>
+      </c>
+      <c r="AB20" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="n">
-        <v>2596946151</v>
+        <v>2666475360</v>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 12:59:54</t>
+          <t>2026-10-09 01:15:01</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 13:35:57</t>
+          <t>2026-10-09 01:34:16</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>36m 3d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F21" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F21" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G21" s="4" t="n">
-        <v>0.01</v>
+        <v>4127.737</v>
       </c>
       <c r="H21" s="4" t="n">
-        <v>4279.52</v>
+        <v>4121.24</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>4271.42</v>
+        <v>-65</v>
       </c>
       <c r="J21" s="4" t="n">
-        <v>4299.72</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>4279.72</v>
-      </c>
-      <c r="L21" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M21" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N21" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+        <v>-6.5</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L21" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M21" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P21" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R21" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4121.24 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 19m 15d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 01:34:16</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="n">
+        <v>4121.11</v>
+      </c>
+      <c r="W21" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X21" s="4" t="n">
+        <v>-66.3</v>
+      </c>
+      <c r="Y21" s="4" t="inlineStr">
+        <is>
+          <t>19m 15d</t>
+        </is>
+      </c>
+      <c r="Z21" s="4" t="n">
+        <v>4121.24</v>
+      </c>
+      <c r="AA21" s="4" t="n">
+        <v>4136.24</v>
+      </c>
+      <c r="AB21" s="4" t="inlineStr">
+        <is>
           <t>Hit Stop Loss (SL)</t>
-        </is>
-      </c>
-      <c r="P21" s="4" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
-        </is>
-      </c>
-      <c r="Q21" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_A-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R21" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Diag</t>
-        </is>
-      </c>
-      <c r="S21" s="4" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="T21" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U21" s="4" t="inlineStr">
-        <is>
-          <t>NORMAL</t>
-        </is>
-      </c>
-      <c r="V21" s="4" t="n">
-        <v>70.93544961398436</v>
-      </c>
-      <c r="W21" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X21" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
-      </c>
-      <c r="Y21" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-24 13:35:58</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="n">
-        <v>2597157735</v>
+        <v>2666586904</v>
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 13:44:55</t>
+          <t>2026-10-09 02:00:00</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 14:50:04</t>
+          <t>2026-10-09 02:03:17</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>1j 5m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F22" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F22" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G22" s="4" t="n">
-        <v>0.01</v>
+        <v>4126.929999999999</v>
       </c>
       <c r="H22" s="4" t="n">
-        <v>4278.702</v>
+        <v>4127.13</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>4271.302</v>
+        <v>2</v>
       </c>
       <c r="J22" s="4" t="n">
-        <v>4297.202</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>4278.902</v>
-      </c>
-      <c r="L22" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M22" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N22" s="8" t="inlineStr">
-        <is>
-          <t>WIN</t>
+      <c r="K22" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q22" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R22" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R22" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S22" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-09 02:00), harga close $4127.05 (di ATAS entry $4126.93, +1.2 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T22" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U22" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 02:03:17</t>
         </is>
       </c>
       <c r="V22" s="4" t="n">
-        <v>68.00231861507318</v>
+        <v>4127.05</v>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X22" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X22" s="4" t="n">
+        <v>1.2</v>
       </c>
       <c r="Y22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 14:50:07</t>
+          <t>3m 17d</t>
+        </is>
+      </c>
+      <c r="Z22" s="4" t="n">
+        <v>4120.67</v>
+      </c>
+      <c r="AA22" s="4" t="n">
+        <v>4135.67</v>
+      </c>
+      <c r="AB22" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="n">
-        <v>2597949075</v>
+        <v>2666709627</v>
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14:55</t>
+          <t>2026-10-09 03:00:00</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:23</t>
+          <t>2026-10-09 03:30:08</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>15m 28d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F23" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F23" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G23" s="4" t="n">
-        <v>0.01</v>
+        <v>4133.611</v>
       </c>
       <c r="H23" s="4" t="n">
-        <v>4263.299</v>
+        <v>4133.81</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>4254.865</v>
+        <v>2</v>
       </c>
       <c r="J23" s="4" t="n">
-        <v>4284.565</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>4254.865</v>
-      </c>
-      <c r="L23" s="4" t="n">
-        <v>-84.3</v>
-      </c>
-      <c r="M23" s="4" t="n">
-        <v>-8.43</v>
-      </c>
-      <c r="N23" s="7" t="inlineStr">
-        <is>
-          <t>LOSS</t>
+        <v>0.2</v>
+      </c>
+      <c r="K23" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q23" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_A-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr">
-        <is>
-          <t>Zona A-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R23" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S23" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-09 03:30), harga close $4133.73 (di ATAS entry $4133.61, +1.2 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
         </is>
       </c>
       <c r="T23" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
         </is>
       </c>
       <c r="U23" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 03:30:08</t>
         </is>
       </c>
       <c r="V23" s="4" t="n">
-        <v>59.28084784842216</v>
+        <v>4133.73</v>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ❌ [ANALISIS KESALAHAN]: Stop Loss tersentuh | KESALAHAN: Entry melawan arah tren utama H4</t>
-        </is>
-      </c>
-      <c r="X23" s="4" t="inlineStr">
-        <is>
-          <t>Hindari entry tanpa konfluensi tren H4, pastikan ruang SL memiliki jarak aman dari noise wick.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X23" s="4" t="n">
+        <v>1.2</v>
       </c>
       <c r="Y23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 16:30:24</t>
+          <t>30m 8d</t>
+        </is>
+      </c>
+      <c r="Z23" s="4" t="n">
+        <v>4127.23</v>
+      </c>
+      <c r="AA23" s="4" t="n">
+        <v>4142.23</v>
+      </c>
+      <c r="AB23" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="n">
-        <v>2598448052</v>
+        <v>2666776150</v>
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:44:54</t>
+          <t>2026-10-09 03:45:01</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:51:29</t>
+          <t>2026-10-09 05:00:36</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>6m 35d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F24" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F24" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G24" s="4" t="n">
-        <v>0.01</v>
+        <v>4133.746</v>
       </c>
       <c r="H24" s="4" t="n">
-        <v>4259.055</v>
+        <v>4134.856</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>4251.492</v>
+        <v>11.1</v>
       </c>
       <c r="J24" s="4" t="n">
-        <v>4274.292</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>4259.255</v>
-      </c>
-      <c r="L24" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N24" s="8" t="inlineStr">
+        <v>1.11</v>
+      </c>
+      <c r="K24" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q24" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R24" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R24" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S24" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Posisi ditutup profit $1.11 di $4134.86 (+11.1 pip dari entry $4133.75) | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4134.25, deviasi +5.0 pip searah BUY).</t>
         </is>
       </c>
       <c r="T24" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U24" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 05:00:36</t>
         </is>
       </c>
       <c r="V24" s="4" t="n">
-        <v>53.32215189379411</v>
+        <v>4134.25</v>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X24" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X24" s="4" t="n">
+        <v>5</v>
       </c>
       <c r="Y24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 17:51:31</t>
+          <t>1j 15m</t>
+        </is>
+      </c>
+      <c r="Z24" s="4" t="n">
+        <v>4127.25</v>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>4142.25</v>
+      </c>
+      <c r="AB24" s="4" t="inlineStr">
+        <is>
+          <t>Close_Thesis 75M Horizon E</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="n">
-        <v>2600157994</v>
+        <v>2666842976</v>
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 22:44:54</t>
+          <t>2026-10-09 05:15:00</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 22:55:44</t>
+          <t>2026-10-09 05:58:53</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>10m 50d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F25" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F25" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G25" s="4" t="n">
-        <v>0.01</v>
+        <v>4133.324</v>
       </c>
       <c r="H25" s="4" t="n">
-        <v>4255.261</v>
+        <v>4137.82</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>4247.661</v>
+        <v>45</v>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4270.461</v>
-      </c>
-      <c r="K25" s="4" t="n">
-        <v>4255.461</v>
-      </c>
-      <c r="L25" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="M25" s="4" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="N25" s="8" t="inlineStr">
+        <v>4.5</v>
+      </c>
+      <c r="K25" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>Hit Stop Loss (SL)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Trend-Aware + ADX + Volume)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q25" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R25" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S25" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +45.0 pip (exit di $4137.82) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4137.94, deviasi +46.2 pip searah BUY).</t>
         </is>
       </c>
       <c r="T25" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U25" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 05:58:53</t>
         </is>
       </c>
       <c r="V25" s="4" t="n">
-        <v>52.57343424140765</v>
+        <v>4137.94</v>
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif</t>
-        </is>
-      </c>
-      <c r="X25" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X25" s="4" t="n">
+        <v>46.2</v>
       </c>
       <c r="Y25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 22:55:46</t>
+          <t>43m 53d</t>
+        </is>
+      </c>
+      <c r="Z25" s="4" t="n">
+        <v>4126.82</v>
+      </c>
+      <c r="AA25" s="4" t="n">
+        <v>4141.82</v>
+      </c>
+      <c r="AB25" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="n">
-        <v>2600228870</v>
+        <v>2667205446</v>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 22:59:54</t>
+          <t>2026-10-09 08:00:00</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 23:16:17</t>
+          <t>2026-10-09 08:06:02</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>16m 23d</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>XAUUSD</t>
-        </is>
-      </c>
-      <c r="F26" s="4" t="inlineStr">
-        <is>
           <t>BUY</t>
         </is>
       </c>
+      <c r="F26" s="4" t="n">
+        <v>0.01</v>
+      </c>
       <c r="G26" s="4" t="n">
-        <v>0.01</v>
+        <v>4143.276</v>
       </c>
       <c r="H26" s="4" t="n">
-        <v>4256.853</v>
+        <v>4147.78</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>4249.253</v>
+        <v>45</v>
       </c>
       <c r="J26" s="4" t="n">
-        <v>4272.053</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>4272.053</v>
-      </c>
-      <c r="L26" s="4" t="n">
-        <v>152</v>
-      </c>
-      <c r="M26" s="4" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
+        <v>4.5</v>
+      </c>
+      <c r="K26" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
+      <c r="L26" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M26" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Hit Take Profit (TP)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
+          <t>UNKNOWN</t>
         </is>
       </c>
       <c r="Q26" s="4" t="inlineStr">
         <is>
-          <t>M15_ZONA_B-Diag_BUY</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr">
-        <is>
-          <t>Zona B-Diag</t>
-        </is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R26" s="4" t="n">
+        <v>50</v>
       </c>
       <c r="S26" s="4" t="inlineStr">
         <is>
-          <t>BEAR</t>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +45.0 pip (exit di $4147.78) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4148.05, deviasi +47.7 pip searah BUY).</t>
         </is>
       </c>
       <c r="T26" s="4" t="inlineStr">
         <is>
-          <t>UNKNOWN</t>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
         </is>
       </c>
       <c r="U26" s="4" t="inlineStr">
         <is>
-          <t>NORMAL</t>
+          <t>2026-10-09 08:06:02</t>
         </is>
       </c>
       <c r="V26" s="4" t="n">
-        <v>53.36517021036406</v>
+        <v>4148.05</v>
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Target Take Profit (TP) tercapai penuh secara sniper</t>
-        </is>
-      </c>
-      <c r="X26" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X26" s="4" t="n">
+        <v>47.7</v>
       </c>
       <c r="Y26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 23:18:20</t>
+          <t>6m 2d</t>
+        </is>
+      </c>
+      <c r="Z26" s="4" t="n">
+        <v>4136.78</v>
+      </c>
+      <c r="AA26" s="4" t="n">
+        <v>4151.78</v>
+      </c>
+      <c r="AB26" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="n">
-        <v>2600670946</v>
+        <v>2667364355</v>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24 23:59:54</t>
+          <t>2026-10-09 08:30:00</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-25 01:25:34</t>
+          <t>2026-10-09 08:41:48</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>1j 25m</t>
+          <t>XAUUSD</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G27" s="4" t="n">
+        <v>4162.025</v>
+      </c>
+      <c r="H27" s="4" t="n">
+        <v>4173.02</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="J27" s="4" t="n">
+        <v>10.99</v>
+      </c>
+      <c r="K27" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R27" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Target Take Profit (TP) $4173.02 tercapai penuh dalam 11m 48d | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4173.69, deviasi +116.6 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:41:48</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="n">
+        <v>4173.69</v>
+      </c>
+      <c r="W27" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X27" s="4" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="Y27" s="4" t="inlineStr">
+        <is>
+          <t>11m 48d</t>
+        </is>
+      </c>
+      <c r="Z27" s="4" t="n">
+        <v>4155.52</v>
+      </c>
+      <c r="AA27" s="4" t="n">
+        <v>4173.02</v>
+      </c>
+      <c r="AB27" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>2667450057</v>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:45:01</t>
+        </is>
+      </c>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 08:54:57</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
           <t>XAUUSD</t>
         </is>
       </c>
-      <c r="F27" s="4" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n">
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="n">
         <v>0.01</v>
       </c>
-      <c r="H27" s="4" t="n">
-        <v>4273.707</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>4282.596</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>4253.696</v>
-      </c>
-      <c r="K27" s="4" t="n">
-        <v>4273.507</v>
-      </c>
-      <c r="L27" s="4" t="n">
+      <c r="G28" s="4" t="n">
+        <v>4169.967</v>
+      </c>
+      <c r="H28" s="4" t="n">
+        <v>4171.97</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J28" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="M27" s="4" t="n">
+      <c r="K28" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R28" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4171.97) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4174.72, deviasi +47.5 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:00:00</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="n">
+        <v>4174.72</v>
+      </c>
+      <c r="W28" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X28" s="4" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="Y28" s="4" t="inlineStr">
+        <is>
+          <t>9m 56d</t>
+        </is>
+      </c>
+      <c r="Z28" s="4" t="n">
+        <v>4163.47</v>
+      </c>
+      <c r="AA28" s="4" t="n">
+        <v>4180.97</v>
+      </c>
+      <c r="AB28" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>2667496882</v>
+      </c>
+      <c r="B29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:00:00</t>
+        </is>
+      </c>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45:01</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G29" s="4" t="n">
+        <v>4174.883</v>
+      </c>
+      <c r="H29" s="4" t="n">
+        <v>4175.08</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J29" s="4" t="n">
         <v>0.2</v>
       </c>
-      <c r="N27" s="8" t="inlineStr">
+      <c r="K29" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R29" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-09 09:45), harga close $4174.87 (di ATAS entry $4174.88, +0.1 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 09:45:01</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="n">
+        <v>4174.87</v>
+      </c>
+      <c r="W29" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X29" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Y29" s="4" t="inlineStr">
+        <is>
+          <t>45m 1d</t>
+        </is>
+      </c>
+      <c r="Z29" s="4" t="n">
+        <v>4168.38</v>
+      </c>
+      <c r="AA29" s="4" t="n">
+        <v>4185.88</v>
+      </c>
+      <c r="AB29" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>2667700534</v>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 10:00:00</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:14:00</t>
+        </is>
+      </c>
+      <c r="D30" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G30" s="4" t="n">
+        <v>4178.237</v>
+      </c>
+      <c r="H30" s="4" t="n">
+        <v>4179.363</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>11.3</v>
+      </c>
+      <c r="J30" s="4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="K30" s="7" t="inlineStr">
         <is>
           <t>WIN</t>
         </is>
       </c>
-      <c r="O27" s="4" t="inlineStr">
+      <c r="L30" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M30" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O30" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P30" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R30" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Posisi ditutup profit $1.12 di $4179.36 (+11.3 pip dari entry $4178.24) | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4179.40, deviasi +11.6 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:14:01</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="n">
+        <v>4179.4</v>
+      </c>
+      <c r="W30" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X30" s="4" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="Y30" s="4" t="inlineStr">
+        <is>
+          <t>1j 14m</t>
+        </is>
+      </c>
+      <c r="Z30" s="4" t="n">
+        <v>4171.74</v>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>4189.24</v>
+      </c>
+      <c r="AB30" s="4" t="inlineStr">
+        <is>
+          <t>Close_Thesis 75M Horizon E</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>2667904599</v>
+      </c>
+      <c r="B31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:15:00</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:44:08</t>
+        </is>
+      </c>
+      <c r="D31" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G31" s="4" t="n">
+        <v>4179.866</v>
+      </c>
+      <c r="H31" s="4" t="n">
+        <v>4181.87</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J31" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K31" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L31" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M31" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O31" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P31" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R31" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4181.87) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4181.87, deviasi +20.0 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:44:07</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="n">
+        <v>4181.87</v>
+      </c>
+      <c r="W31" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X31" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y31" s="4" t="inlineStr">
+        <is>
+          <t>29m 8d</t>
+        </is>
+      </c>
+      <c r="Z31" s="4" t="n">
+        <v>4173.37</v>
+      </c>
+      <c r="AA31" s="4" t="n">
+        <v>4190.87</v>
+      </c>
+      <c r="AB31" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>2667996875</v>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 11:45:02</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:04:30</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G32" s="4" t="n">
+        <v>4181.521</v>
+      </c>
+      <c r="H32" s="4" t="n">
+        <v>4183.52</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J32" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K32" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L32" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M32" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O32" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P32" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R32" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4183.52) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4183.89, deviasi +23.7 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:04:31</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="n">
+        <v>4183.89</v>
+      </c>
+      <c r="W32" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X32" s="4" t="n">
+        <v>23.7</v>
+      </c>
+      <c r="Y32" s="4" t="inlineStr">
+        <is>
+          <t>19m 28d</t>
+        </is>
+      </c>
+      <c r="Z32" s="4" t="n">
+        <v>4175.02</v>
+      </c>
+      <c r="AA32" s="4" t="n">
+        <v>4192.52</v>
+      </c>
+      <c r="AB32" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>2668200363</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:30:01</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:36:35</t>
+        </is>
+      </c>
+      <c r="D33" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G33" s="4" t="n">
+        <v>4193.641</v>
+      </c>
+      <c r="H33" s="4" t="n">
+        <v>4204.64</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>110</v>
+      </c>
+      <c r="J33" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="K33" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L33" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M33" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O33" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P33" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R33" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Target Take Profit (TP) $4204.64 tercapai penuh dalam 6m 34d | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4202.20, deviasi +85.6 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:45:00</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="n">
+        <v>4202.2</v>
+      </c>
+      <c r="W33" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X33" s="4" t="n">
+        <v>85.59999999999999</v>
+      </c>
+      <c r="Y33" s="4" t="inlineStr">
+        <is>
+          <t>6m 34d</t>
+        </is>
+      </c>
+      <c r="Z33" s="4" t="n">
+        <v>4187.14</v>
+      </c>
+      <c r="AA33" s="4" t="n">
+        <v>4204.64</v>
+      </c>
+      <c r="AB33" s="4" t="inlineStr">
+        <is>
+          <t>Hit Take Profit (TP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>2668327566</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:45:01</t>
+        </is>
+      </c>
+      <c r="C34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 12:53:03</t>
+        </is>
+      </c>
+      <c r="D34" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G34" s="4" t="n">
+        <v>4202.08</v>
+      </c>
+      <c r="H34" s="4" t="n">
+        <v>4195.58</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>-65</v>
+      </c>
+      <c r="J34" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K34" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L34" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M34" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O34" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P34" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R34" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4195.58 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 8m 2d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:00:00</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="n">
+        <v>4193.06</v>
+      </c>
+      <c r="W34" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X34" s="4" t="n">
+        <v>-90.2</v>
+      </c>
+      <c r="Y34" s="4" t="inlineStr">
+        <is>
+          <t>8m 2d</t>
+        </is>
+      </c>
+      <c r="Z34" s="4" t="n">
+        <v>4195.58</v>
+      </c>
+      <c r="AA34" s="4" t="n">
+        <v>4213.08</v>
+      </c>
+      <c r="AB34" s="4" t="inlineStr">
         <is>
           <t>Hit Stop Loss (SL)</t>
         </is>
       </c>
-      <c r="P27" s="4" t="inlineStr">
-        <is>
-          <t>LightGBM M15 v4.1 (Structural RRR + 30D HTF)</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>M15_ZONA_C_SELL</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr">
-        <is>
-          <t>Zona C</t>
-        </is>
-      </c>
-      <c r="S27" s="4" t="inlineStr">
-        <is>
-          <t>BEAR</t>
-        </is>
-      </c>
-      <c r="T27" s="4" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="U27" s="4" t="inlineStr">
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>2668414184</v>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:00:00</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:06:10</t>
+        </is>
+      </c>
+      <c r="D35" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G35" s="4" t="n">
+        <v>4193.567999999999</v>
+      </c>
+      <c r="H35" s="4" t="n">
+        <v>4195.57</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K35" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L35" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M35" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O35" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P35" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr">
         <is>
           <t>NORMAL</t>
         </is>
       </c>
-      <c r="V27" s="4" t="n">
-        <v>54.19185017665952</v>
-      </c>
-      <c r="W27" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> ✅ [FAKTOR KEMENANGAN]: Exit profit positif | Didukung penuh tren besar H4 (Searah Trend Institusional)</t>
-        </is>
-      </c>
-      <c r="X27" s="4" t="inlineStr">
-        <is>
-          <t>Skenario ini terbukti efektif. Pertahankan konfluensi multi-timeframe dan disiplin hold hingga target.</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-25 01:25:38</t>
+      <c r="R35" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4195.57) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4196.62, deviasi +30.5 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:06:10</t>
+        </is>
+      </c>
+      <c r="V35" s="4" t="n">
+        <v>4196.62</v>
+      </c>
+      <c r="W35" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X35" s="4" t="n">
+        <v>30.5</v>
+      </c>
+      <c r="Y35" s="4" t="inlineStr">
+        <is>
+          <t>6m 10d</t>
+        </is>
+      </c>
+      <c r="Z35" s="4" t="n">
+        <v>4187.07</v>
+      </c>
+      <c r="AA35" s="4" t="n">
+        <v>4204.57</v>
+      </c>
+      <c r="AB35" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>2668504472</v>
+      </c>
+      <c r="B36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:15:00</t>
+        </is>
+      </c>
+      <c r="C36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:21:11</t>
+        </is>
+      </c>
+      <c r="D36" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G36" s="4" t="n">
+        <v>4192.215999999999</v>
+      </c>
+      <c r="H36" s="4" t="n">
+        <v>4192.42</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="4" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K36" s="6" t="inlineStr">
+        <is>
+          <t>BEP_REBOUND</t>
+        </is>
+      </c>
+      <c r="L36" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M36" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O36" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P36" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R36" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>🔄 [BEP REBOUND — Berhasil Arah, Exit Dini]: Posisi terkena Auto Break-Even (+0.20) akibat proteksi BEP, namun PREDIKSI MODEL TERBUKTI VALID: pada candle ke-5 (2026-10-09 13:15), harga close $4192.21 (di ATAS entry $4192.22, +0.1 pip) | Trailing lock mengamankan modal sebelum retracement sesaat; harga melanjutkan arah | Skenario 'GENERAL_ENTRY' secara ARAH dinilai BERHASIL meski exit lebih awal karena BEP.</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>Model prediksi AKURAT secara arah pada skenario GENERAL_ENTRY. Pertimbangkan SL sedikit lebih lebar agar BEP tidak aktif terlalu dini pada kondisi volatile yang tetap bearah prediksi.</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:21:11</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="n">
+        <v>4192.21</v>
+      </c>
+      <c r="W36" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X36" s="4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="Y36" s="4" t="inlineStr">
+        <is>
+          <t>6m 11d</t>
+        </is>
+      </c>
+      <c r="Z36" s="4" t="n">
+        <v>4185.72</v>
+      </c>
+      <c r="AA36" s="4" t="n">
+        <v>4203.22</v>
+      </c>
+      <c r="AB36" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>2668565879</v>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 13:30:00</t>
+        </is>
+      </c>
+      <c r="C37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:06:56</t>
+        </is>
+      </c>
+      <c r="D37" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G37" s="4" t="n">
+        <v>4190.401</v>
+      </c>
+      <c r="H37" s="4" t="n">
+        <v>4194.9</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J37" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K37" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L37" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M37" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O37" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P37" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R37" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +45.0 pip (exit di $4194.90) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4194.76, deviasi +43.6 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:06:56</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="n">
+        <v>4194.76</v>
+      </c>
+      <c r="W37" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X37" s="4" t="n">
+        <v>43.6</v>
+      </c>
+      <c r="Y37" s="4" t="inlineStr">
+        <is>
+          <t>36m 56d</t>
+        </is>
+      </c>
+      <c r="Z37" s="4" t="n">
+        <v>4183.87</v>
+      </c>
+      <c r="AA37" s="4" t="n">
+        <v>4201.37</v>
+      </c>
+      <c r="AB37" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>2668741932</v>
+      </c>
+      <c r="B38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 14:15:01</t>
+        </is>
+      </c>
+      <c r="C38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:23:33</t>
+        </is>
+      </c>
+      <c r="D38" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>4194.257</v>
+      </c>
+      <c r="H38" s="4" t="n">
+        <v>4198.76</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>45</v>
+      </c>
+      <c r="J38" s="4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K38" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L38" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M38" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O38" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P38" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R38" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +45.0 pip (exit di $4198.76) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4198.66, deviasi +44.0 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:23:33</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="n">
+        <v>4198.66</v>
+      </c>
+      <c r="W38" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X38" s="4" t="n">
+        <v>44</v>
+      </c>
+      <c r="Y38" s="4" t="inlineStr">
+        <is>
+          <t>1j 8m</t>
+        </is>
+      </c>
+      <c r="Z38" s="4" t="n">
+        <v>4187.76</v>
+      </c>
+      <c r="AA38" s="4" t="n">
+        <v>4202.76</v>
+      </c>
+      <c r="AB38" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>2669044711</v>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:30:00</t>
+        </is>
+      </c>
+      <c r="C39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:40:03</t>
+        </is>
+      </c>
+      <c r="D39" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G39" s="4" t="n">
+        <v>4198.815</v>
+      </c>
+      <c r="H39" s="4" t="n">
+        <v>4192.31</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>-65</v>
+      </c>
+      <c r="J39" s="4" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="K39" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L39" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M39" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O39" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P39" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R39" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4192.31 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 10m 3d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:40:04</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="n">
+        <v>4192.47</v>
+      </c>
+      <c r="W39" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X39" s="4" t="n">
+        <v>-63.4</v>
+      </c>
+      <c r="Y39" s="4" t="inlineStr">
+        <is>
+          <t>10m 3d</t>
+        </is>
+      </c>
+      <c r="Z39" s="4" t="n">
+        <v>4192.31</v>
+      </c>
+      <c r="AA39" s="4" t="n">
+        <v>4207.31</v>
+      </c>
+      <c r="AB39" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>2669112654</v>
+      </c>
+      <c r="B40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 15:45:01</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:16:06</t>
+        </is>
+      </c>
+      <c r="D40" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G40" s="4" t="n">
+        <v>4191.523999999999</v>
+      </c>
+      <c r="H40" s="4" t="n">
+        <v>4185.02</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>-65</v>
+      </c>
+      <c r="J40" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K40" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L40" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M40" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O40" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P40" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R40" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4185.02 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 31m 5d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:16:07</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="n">
+        <v>4184.67</v>
+      </c>
+      <c r="W40" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X40" s="4" t="n">
+        <v>-68.5</v>
+      </c>
+      <c r="Y40" s="4" t="inlineStr">
+        <is>
+          <t>31m 5d</t>
+        </is>
+      </c>
+      <c r="Z40" s="4" t="n">
+        <v>4185.02</v>
+      </c>
+      <c r="AA40" s="4" t="n">
+        <v>4200.02</v>
+      </c>
+      <c r="AB40" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>2669286385</v>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 16:30:00</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:43:18</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>4187.301</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>4180.8</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>-65</v>
+      </c>
+      <c r="J41" s="4" t="n">
+        <v>-6.5</v>
+      </c>
+      <c r="K41" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M41" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O41" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P41" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R41" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4180.80 tersentuh — harga bergerak 65.0 pip melawan posisi dalam 1j 13m | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 17:43:18</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="n">
+        <v>4180.68</v>
+      </c>
+      <c r="W41" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X41" s="4" t="n">
+        <v>-66.2</v>
+      </c>
+      <c r="Y41" s="4" t="inlineStr">
+        <is>
+          <t>1j 13m</t>
+        </is>
+      </c>
+      <c r="Z41" s="4" t="n">
+        <v>4180.8</v>
+      </c>
+      <c r="AA41" s="4" t="n">
+        <v>4195.8</v>
+      </c>
+      <c r="AB41" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>2669696905</v>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 18:30:00</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:33:00</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>4184.367</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>4186.37</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J42" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K42" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M42" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O42" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P42" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q42" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4186.37) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4186.31, deviasi +19.4 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 19:33:01</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="n">
+        <v>4186.31</v>
+      </c>
+      <c r="W42" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X42" s="4" t="n">
+        <v>19.4</v>
+      </c>
+      <c r="Y42" s="4" t="inlineStr">
+        <is>
+          <t>1j 3m</t>
+        </is>
+      </c>
+      <c r="Z42" s="4" t="n">
+        <v>4177.87</v>
+      </c>
+      <c r="AA42" s="4" t="n">
+        <v>4192.87</v>
+      </c>
+      <c r="AB42" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
         </is>
       </c>
     </row>

--- a/Evaluasi_Skenario_Trade.xlsx
+++ b/Evaluasi_Skenario_Trade.xlsx
@@ -649,10 +649,10 @@
         </is>
       </c>
       <c r="B5" s="5" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C5" s="5" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D5" s="5" t="n">
         <v>9</v>
@@ -661,25 +661,25 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>73.7</v>
+        <v>73.2</v>
       </c>
       <c r="H5" s="5" t="n">
-        <v>34.99</v>
+        <v>32.84</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>0.92</v>
+        <v>0.8</v>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>[28/10 Win]</t>
+          <t>[30/10 Win]</t>
         </is>
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>[9/10 Loss]</t>
+          <t>[10/10 Loss]</t>
         </is>
       </c>
       <c r="L5" s="6" t="inlineStr">
@@ -709,7 +709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB42"/>
+  <dimension ref="A1:AB45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="55" customWidth="1" min="1" max="1"/>
@@ -5459,6 +5459,366 @@
         </is>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>2670573269</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:00:01</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:22:13</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>4190.552</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>-61.5</v>
+      </c>
+      <c r="J43" s="4" t="n">
+        <v>-6.15</v>
+      </c>
+      <c r="K43" s="9" t="inlineStr">
+        <is>
+          <t>LOSS</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M43" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O43" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P43" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q43" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>❌ [LOSS — Analisis Kesalahan]: Stop Loss $4184.40 tersentuh — harga bergerak 61.5 pip melawan posisi dalam 22m 12d | Keyakinan model di batas bawah (50.0%) — entry berisiko tanpa konfluensi penuh.</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>Untuk skenario GENERAL_ENTRY: Pastikan konfluensi H4 searah sebelum entry. SL minimal 35-50 pip dari entry. Hindari entry jika probabilitas model &lt; 62%.</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 21:22:14</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="n">
+        <v>4184.28</v>
+      </c>
+      <c r="W43" s="4" t="inlineStr">
+        <is>
+          <t>GAGAL (TIDAK SELARAS)</t>
+        </is>
+      </c>
+      <c r="X43" s="4" t="n">
+        <v>-62.7</v>
+      </c>
+      <c r="Y43" s="4" t="inlineStr">
+        <is>
+          <t>22m 12d</t>
+        </is>
+      </c>
+      <c r="Z43" s="4" t="n">
+        <v>4184.4</v>
+      </c>
+      <c r="AA43" s="4" t="n">
+        <v>4199.4</v>
+      </c>
+      <c r="AB43" s="4" t="inlineStr">
+        <is>
+          <t>Hit Stop Loss (SL)</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>2670966805</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:15:00</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:45:48</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>4185.293</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>4187.29</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J44" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K44" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M44" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O44" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P44" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q44" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4187.29) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4187.54, deviasi +22.5 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 22:45:49</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="n">
+        <v>4187.54</v>
+      </c>
+      <c r="W44" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X44" s="4" t="n">
+        <v>22.5</v>
+      </c>
+      <c r="Y44" s="4" t="inlineStr">
+        <is>
+          <t>30m 48d</t>
+        </is>
+      </c>
+      <c r="Z44" s="4" t="n">
+        <v>4178.79</v>
+      </c>
+      <c r="AA44" s="4" t="n">
+        <v>4193.79</v>
+      </c>
+      <c r="AB44" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>2671148498</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:00:00</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:19:29</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>XAUUSD</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>4188.831</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>4190.83</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="J45" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="K45" s="7" t="inlineStr">
+        <is>
+          <t>WIN</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>LightGBM v5.2 SMC/DXY M15 (65 Fitur)</t>
+        </is>
+      </c>
+      <c r="M45" s="4" t="inlineStr">
+        <is>
+          <t>GENERAL_ENTRY</t>
+        </is>
+      </c>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>ZONA_UNKNOWN</t>
+        </is>
+      </c>
+      <c r="O45" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="P45" s="4" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr">
+        <is>
+          <t>NORMAL</t>
+        </is>
+      </c>
+      <c r="R45" s="4" t="n">
+        <v>50</v>
+      </c>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>✅ [WIN — Kemenangan Target]: Trailing profit lock berhasil mengamankan +20.0 pip (exit di $4190.83) sebelum harga berbalik | Validasi Model 75M: SELARAS BERHASIL (Close bar-5: $4191.00, deviasi +21.7 pip searah BUY).</t>
+        </is>
+      </c>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>Skenario GENERAL_ENTRY terbukti valid (H4=UNKNOWN, DXY=UNKNOWN). Pertahankan konfluensi multi-timeframe dan disiplin hold hingga TP.</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-09 23:19:30</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="n">
+        <v>4191</v>
+      </c>
+      <c r="W45" s="4" t="inlineStr">
+        <is>
+          <t>BERHASIL (SELARAS)</t>
+        </is>
+      </c>
+      <c r="X45" s="4" t="n">
+        <v>21.7</v>
+      </c>
+      <c r="Y45" s="4" t="inlineStr">
+        <is>
+          <t>19m 29d</t>
+        </is>
+      </c>
+      <c r="Z45" s="4" t="n">
+        <v>4182.33</v>
+      </c>
+      <c r="AA45" s="4" t="n">
+        <v>4197.33</v>
+      </c>
+      <c r="AB45" s="4" t="inlineStr">
+        <is>
+          <t>Trailing Lock (BEP +$0.20)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
